--- a/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
+++ b/BWI/bestwine_output/bestwine_Bosnia and Herzegovina.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1822,6 +1822,1117 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>D.o.o. Dukat Banja Luka</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>D.o.o. Dukat Banja Luka</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>123050</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Aleksandrovac</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Republika Srpska</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Aleksandrovac Bb Industrial Zone</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>78255</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://dukat-bih.com</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>b.luka@dukat-bih.com</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>+387 51 582-440</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>4400842150003</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@dukatbih9312/</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Predrag Gataric</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/predrag-gataric-356216177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>D.o.o. Dukat Banja Luka</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>D.o.o. Dukat Banja Luka</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>123050</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Aleksandrovac</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Republika Srpska</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Aleksandrovac Bb Industrial Zone</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78255</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://dukat-bih.com</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>b.luka@dukat-bih.com</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>+387 51 582-440</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>4400842150003</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@dukatbih9312/</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Faruk Ramic</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Sales</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/faruk-ramic-4a4452170/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Fina Vina D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Fina Vina D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>20163</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Kanton Sarajevo</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>70b Radnička</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.finavina.ba</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>info@finavina.ba</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>4201632910002</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fina-vina/</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/finavinabih/</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/finavina.ba/</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Lejla Besirevic</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>Director Of Sales Marketing</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lejla-besirevic/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Fina Vina D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Fina Vina D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>20163</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Kanton Sarajevo</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>70b Radnička</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.finavina.ba</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>info@finavina.ba</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>4201632910002</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fina-vina/</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/finavinabih/</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/finavina.ba/</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Primož Vilfan</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/primo%c5%be-vilfan-34962952/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Belamionix D.o.o.</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Belamionix D.o.o.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>91173</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Brčko</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Brčko Distrikt</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>bb Sulje Kahrimana</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76100</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://belamionix.ba, https://belashop.ba</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>info@belamionix.ba</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>+387 49 746-096</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>4600208840004</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/belamionixdoo</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/belamionix.doo</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="2" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Binvest D.o.o. Posusje</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Binvest D.o.o. Posusje</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>19361</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Posusje</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Zapadnohercegovački kanton</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Ričina Br. 2</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>88240</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://binvest-po.com</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>info@binvest-po.com</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>+387 39 682-350</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>4272004600007</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/binvest-d-o-o-/</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/binvest</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/binvestdoo/</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UChW9b9tKDU09E6o14NTuSwA</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Marko Puljić</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Procurement</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/marko-pulji%c4%87-0b61421a5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Binvest D.o.o. Posusje</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Binvest D.o.o. Posusje</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>19361</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Posusje</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Zapadnohercegovački kanton</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Ričina Br. 2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>88240</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://binvest-po.com</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>info@binvest-po.com</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>+387 39 682-350</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>4272004600007</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/binvest-d-o-o-/</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/binvest</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/binvestdoo/</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UChW9b9tKDU09E6o14NTuSwA</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Ivica Šušnjar</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ivica-%c5%a1u%c5%a1njar-ba89396b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Venera D.o.o. Banja Luka</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Venera D.o.o. Banja Luka</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Banja Luka</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Republika Srpska</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>bb Blagoja Parovića</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>78000</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://venera.ba</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>info@venera.ba</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>+387 51 388-972</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>4400849670002</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/venera-d-o-o/</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/venera-banja-luka-964004040311516</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/venerabih/</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Tihomir Trivunović</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>National Sales Director</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tihomir-trivunović-986691171</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Venera D.o.o. Banja Luka</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Venera D.o.o. Banja Luka</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Banja Luka</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Republika Srpska</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>bb Blagoja Parovića</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>78000</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://venera.ba</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>info@venera.ba</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>+387 51 388-972</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>4400849670002</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/venera-d-o-o/</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/venera-banja-luka-964004040311516</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/venerabih/</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Milos Djurdjevic</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/milos-djurdjevic-00212bb6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Co Trink D.o.o.</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Co Trink D.o.o.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>51731</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Posusje</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Županija Zapadnohercegovačka</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Ante Starčevića Bb</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>88240</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://cotrink.com</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>cotrink@cotrink.com</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>+387 39 682-220</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>4272112320002</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr"/>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Only Vip D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Only Vip D.o.o. Sarajevo</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>47982</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Federacija Bosne i Hercegovine, Kanton Sarajevo</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>A transverzala</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>71000</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://onlyvipsarajevo.com</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>onlyvip.sadovic@gmail.com</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineShopSarajevo/</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineshopsarajevo</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr"/>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
